--- a/Catch models/scenarios_summarize_by_scenario_macarellus_cmsy.xlsx
+++ b/Catch models/scenarios_summarize_by_scenario_macarellus_cmsy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="83">
   <si>
     <t>scenario</t>
   </si>
@@ -37,281 +37,293 @@
     <t>NN_CMSY_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.27 [0.10-0.59]
-0.14 [0.10-0.23]</t>
-  </si>
-  <si>
-    <t>41 [12-103]
-51 [31-77]</t>
-  </si>
-  <si>
-    <t>0.20 [0.07-0.33]
-0.24 [0.11-0.40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.466
- bk = 0.013</t>
+    <t>0.42 [0.20-0.80]
+0.25 [0.17-0.36]</t>
+  </si>
+  <si>
+    <t>19 [7-43]
+21 [15-28]</t>
+  </si>
+  <si>
+    <t>0.12 [0.02-0.22]
+0.11 [0.03-0.22]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.413
+ bk = -0.028</t>
   </si>
   <si>
     <t>NN_CMSY_lower resilience</t>
   </si>
   <si>
-    <t>0.16 [0.05-0.39]
+    <t>0.21 [0.05-0.60]
 0.08 [0.05-0.12]</t>
   </si>
   <si>
-    <t>74 [19-205]
-112 [64-168]</t>
-  </si>
-  <si>
-    <t>0.20 [0.07-0.33]
-0.25 [0.13-0.42]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.516
- bk = 0.071</t>
+    <t>51 [10-161]
+90 [48-134]</t>
+  </si>
+  <si>
+    <t>0.12 [0.02-0.22]
+0.14 [0.05-0.26]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.580
+ bk = 0.104</t>
   </si>
   <si>
     <t>NN_CMSY_Higher resilience</t>
   </si>
   <si>
-    <t>0.50 [0.30-0.79]
-0.38 [0.28-0.53]</t>
-  </si>
-  <si>
-    <t>19 [8-37]
-20 [15-26]</t>
-  </si>
-  <si>
-    <t>0.20 [0.07-0.33]
-0.21 [0.09-0.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.251
- bk = -0.052</t>
+    <t>0.65 [0.40-1.00]
+0.46 [0.34-0.65]</t>
+  </si>
+  <si>
+    <t>12 [5-23]
+13 [10-16]</t>
+  </si>
+  <si>
+    <t>0.12 [0.02-0.22]
+0.11 [0.03-0.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.259
+ bk = -0.041</t>
   </si>
   <si>
     <t>NN_CMSY_Non-informative_r</t>
   </si>
   <si>
+    <t>0.48 [0.10-1.50]
+0.14 [0.09-0.23]</t>
+  </si>
+  <si>
+    <t>23 [4-76]
+38 [23-58]</t>
+  </si>
+  <si>
+    <t>0.12 [0.02-0.22]
+0.12 [0.03-0.23]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.632
+ bk = -0.047</t>
+  </si>
+  <si>
+    <t>zBRT_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 [0.20-0.80]
+0.24 [0.17-0.35]</t>
+  </si>
+  <si>
+    <t>19 [7-43]
+22 [15-30]</t>
+  </si>
+  <si>
+    <t>0.20 [0.01-0.39]
+0.26 [0.04-0.55]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.411
+ bk = -0.403</t>
+  </si>
+  <si>
+    <t>zBRT_lower resilience</t>
+  </si>
+  <si>
+    <t>0.21 [0.05-0.60]
+0.07 [0.05-0.12]</t>
+  </si>
+  <si>
+    <t>49 [10-154]
+86 [50-129]</t>
+  </si>
+  <si>
+    <t>0.20 [0.01-0.39]
+0.23 [0.06-0.42]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.574
+ bk = 0.057</t>
+  </si>
+  <si>
+    <t>zBRT_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 [0.40-1.00]
+0.46 [0.35-0.63]</t>
+  </si>
+  <si>
+    <t>0.20 [0.01-0.39]
+0.18 [0.03-0.44]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.303
+ bk = -0.215</t>
+  </si>
+  <si>
+    <t>zBRT_Non-informative_r</t>
+  </si>
+  <si>
     <t>0.49 [0.10-1.50]
-0.15 [0.10-0.24]</t>
-  </si>
-  <si>
-    <t>29 [5-96]
-47 [30-70]</t>
-  </si>
-  <si>
-    <t>0.20 [0.07-0.33]
-0.23 [0.11-0.37]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.625
- bk = 0.060</t>
-  </si>
-  <si>
-    <t>zBRT_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.27 [0.10-0.59]
-0.15 [0.10-0.23]</t>
-  </si>
-  <si>
-    <t>40 [12-100]
-54 [35-79]</t>
-  </si>
-  <si>
-    <t>0.37 [0.05-0.69]
-0.45 [0.23-0.71]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.468
- bk = 0.335</t>
-  </si>
-  <si>
-    <t>zBRT_lower resilience</t>
-  </si>
-  <si>
-    <t>0.16 [0.05-0.39]
-0.08 [0.05-0.13]</t>
-  </si>
-  <si>
-    <t>73 [18-204]
-114 [69-170]</t>
-  </si>
-  <si>
-    <t>0.37 [0.05-0.69]
-0.49 [0.24-0.72]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.518
- bk = 0.327</t>
-  </si>
-  <si>
-    <t>zBRT_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.50 [0.30-0.79]
-0.40 [0.29-0.56]</t>
-  </si>
-  <si>
-    <t>19 [8-38]
-21 [15-28]</t>
-  </si>
-  <si>
-    <t>0.37 [0.05-0.69]
-0.46 [0.19-0.73]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.236
- bk = 0.229</t>
-  </si>
-  <si>
-    <t>zBRT_Non-informative_r</t>
+0.14 [0.09-0.21]</t>
+  </si>
+  <si>
+    <t>24 [4-80]
+42 [25-63]</t>
+  </si>
+  <si>
+    <t>0.20 [0.01-0.39]
+0.23 [0.06-0.45]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.645
+ bk = -0.044</t>
+  </si>
+  <si>
+    <t>Target_switch_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 [0.20-0.80]
+0.25 [0.18-0.37]</t>
+  </si>
+  <si>
+    <t>19 [7-42]
+21 [15-29]</t>
+  </si>
+  <si>
+    <t>0.45 [0.20-0.70]
+0.49 [0.27-0.70]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.413
+ bk = 0.177</t>
+  </si>
+  <si>
+    <t>Target_switch_lower resilience</t>
+  </si>
+  <si>
+    <t>51 [10-156]
+88 [52-131]</t>
+  </si>
+  <si>
+    <t>0.45 [0.20-0.70]
+0.41 [0.23-0.59]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.594
+ bk = 0.288</t>
+  </si>
+  <si>
+    <t>Target_switch_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 [0.40-1.00]
+0.45 [0.34-0.61]</t>
+  </si>
+  <si>
+    <t>0.45 [0.20-0.70]
+0.55 [0.24-0.77]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.303
+ bk = -0.040</t>
+  </si>
+  <si>
+    <t>Target_switch_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.48 [0.10-1.50]
+0.14 [0.09-0.24]</t>
+  </si>
+  <si>
+    <t>24 [4-77]
+39 [22-58]</t>
+  </si>
+  <si>
+    <t>0.45 [0.20-0.70]
+0.42 [0.22-0.60]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.604
+ bk = 0.247</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 [0.20-0.80]
+0.26 [0.18-0.39]</t>
+  </si>
+  <si>
+    <t>19 [7-43]
+21 [15-29]</t>
+  </si>
+  <si>
+    <t>0.51 [0.01-1.00]
+0.54 [0.19-0.87]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.387
+ bk = 0.428</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_lower resilience</t>
+  </si>
+  <si>
+    <t>0.22 [0.05-0.60]
+0.08 [0.05-0.12]</t>
+  </si>
+  <si>
+    <t>49 [10-156]
+86 [51-128]</t>
+  </si>
+  <si>
+    <t>0.51 [0.01-1.00]
+0.36 [0.10-0.66]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.594
+ bk = 0.458</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 [0.40-1.00]
+0.49 [0.35-0.68]</t>
+  </si>
+  <si>
+    <t>12 [5-23]
+12 [9-16]</t>
+  </si>
+  <si>
+    <t>0.51 [0.01-1.00]
+0.66 [0.23-0.95]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.188
+ bk = 0.141</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Non-informative_r</t>
   </si>
   <si>
     <t>0.49 [0.10-1.50]
-0.16 [0.10-0.26]</t>
-  </si>
-  <si>
-    <t>29 [5-96]
-50 [31-72]</t>
-  </si>
-  <si>
-    <t>0.37 [0.05-0.69]
-0.41 [0.19-0.67]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.617
- bk = 0.338</t>
-  </si>
-  <si>
-    <t>Target_switch_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>40 [12-100]
-55 [35-79]</t>
-  </si>
-  <si>
-    <t>0.45 [0.20-0.70]
-0.48 [0.26-0.68]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.472
- bk = 0.189</t>
-  </si>
-  <si>
-    <t>Target_switch_lower resilience</t>
-  </si>
-  <si>
-    <t>73 [19-201]
-113 [71-165]</t>
-  </si>
-  <si>
-    <t>0.45 [0.20-0.70]
-0.49 [0.28-0.69]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.513
- bk = 0.222</t>
-  </si>
-  <si>
-    <t>Target_switch_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.50 [0.30-0.79]
-0.40 [0.30-0.56]</t>
-  </si>
-  <si>
-    <t>19 [8-37]
-21 [15-27]</t>
-  </si>
-  <si>
-    <t>0.45 [0.20-0.70]
-0.48 [0.26-0.69]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.289
- bk = 0.135</t>
-  </si>
-  <si>
-    <t>Target_switch_Non-informative_r</t>
-  </si>
-  <si>
-    <t>28 [5-93]
-50 [31-73]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.610
- bk = 0.189</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.27 [0.10-0.59]
-0.15 [0.10-0.24]</t>
-  </si>
-  <si>
-    <t>41 [12-103]
-56 [35-82]</t>
-  </si>
-  <si>
-    <t>0.51 [0.01-1.00]
-0.52 [0.16-0.82]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.455
- bk = 0.471</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_lower resilience</t>
-  </si>
-  <si>
-    <t>74 [19-201]
-115 [71-168]</t>
+0.15 [0.10-0.25]</t>
+  </si>
+  <si>
+    <t>24 [4-80]
+41 [23-62]</t>
   </si>
   <si>
     <t>0.50 [0.01-1.00]
-0.54 [0.27-0.85]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.489
- bk = 0.504</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.50 [0.30-0.79]
-0.42 [0.30-0.59]</t>
-  </si>
-  <si>
-    <t>19 [8-37]
-21 [15-28]</t>
-  </si>
-  <si>
-    <t>0.50 [0.01-1.00]
-0.54 [0.20-0.86]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.232
- bk = 0.404</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.49 [0.10-1.50]
-0.17 [0.10-0.28]</t>
-  </si>
-  <si>
-    <t>29 [5-95]
-51 [32-75]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.576
- bk = 0.450</t>
+0.44 [0.09-0.75]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.631
+ bk = 0.385</t>
   </si>
 </sst>
 </file>
@@ -694,7 +706,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -714,7 +726,7 @@
         <v>15</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -734,7 +746,7 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>4.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -754,7 +766,7 @@
         <v>25</v>
       </c>
       <c r="F5">
-        <v>4.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -774,7 +786,7 @@
         <v>30</v>
       </c>
       <c r="F6">
-        <v>40.7</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -794,7 +806,7 @@
         <v>35</v>
       </c>
       <c r="F7">
-        <v>45</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -805,44 +817,44 @@
         <v>37</v>
       </c>
       <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
         <v>38</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>39</v>
       </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
       <c r="F8">
-        <v>29.8</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
         <v>41</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>42</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>44</v>
       </c>
-      <c r="E9" t="s">
-        <v>45</v>
-      </c>
       <c r="F9">
-        <v>25.6</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
         <v>46</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
@@ -854,7 +866,7 @@
         <v>49</v>
       </c>
       <c r="F10">
-        <v>38.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -862,7 +874,7 @@
         <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
         <v>51</v>
@@ -874,7 +886,7 @@
         <v>53</v>
       </c>
       <c r="F11">
-        <v>42.7</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -885,116 +897,116 @@
         <v>55</v>
       </c>
       <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
         <v>56</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>57</v>
       </c>
-      <c r="E12" t="s">
-        <v>58</v>
-      </c>
       <c r="F12">
-        <v>29.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
         <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
       </c>
       <c r="C13" t="s">
         <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F13">
-        <v>24.2</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14">
-        <v>79.5</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15">
         <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15">
-        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F16">
-        <v>75.8</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F17">
-        <v>73.3</v>
+        <v>61.9</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/scenarios_summarize_by_scenario_macarellus_cmsy.xlsx
+++ b/Catch models/scenarios_summarize_by_scenario_macarellus_cmsy.xlsx
@@ -37,20 +37,20 @@
     <t>NN_CMSY_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.42 [0.20-0.80]
-0.25 [0.17-0.36]</t>
-  </si>
-  <si>
-    <t>19 [7-43]
-21 [15-28]</t>
-  </si>
-  <si>
-    <t>0.12 [0.02-0.22]
-0.11 [0.03-0.22]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.413
- bk = -0.028</t>
+    <t>0.43 [0.20-0.80]
+0.24 [0.17-0.36]</t>
+  </si>
+  <si>
+    <t>23 [9-53]
+29 [20-37]</t>
+  </si>
+  <si>
+    <t>0.14 [0.03-0.25]
+0.15 [0.04-0.29]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.392
+ bk = -0.089</t>
   </si>
   <si>
     <t>NN_CMSY_lower resilience</t>
@@ -60,270 +60,270 @@
 0.08 [0.05-0.12]</t>
   </si>
   <si>
-    <t>51 [10-161]
-90 [48-134]</t>
-  </si>
-  <si>
-    <t>0.12 [0.02-0.22]
-0.14 [0.05-0.26]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.580
- bk = 0.104</t>
+    <t>63 [12-198]
+107 [59-161]</t>
+  </si>
+  <si>
+    <t>0.14 [0.03-0.25]
+0.18 [0.08-0.31]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.586
+ bk = 0.131</t>
   </si>
   <si>
     <t>NN_CMSY_Higher resilience</t>
   </si>
   <si>
     <t>0.65 [0.40-1.00]
-0.46 [0.34-0.65]</t>
-  </si>
-  <si>
-    <t>12 [5-23]
-13 [10-16]</t>
-  </si>
-  <si>
-    <t>0.12 [0.02-0.22]
-0.11 [0.03-0.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.259
- bk = -0.041</t>
+0.47 [0.36-0.66]</t>
+  </si>
+  <si>
+    <t>14 [6-29]
+17 [13-21]</t>
+  </si>
+  <si>
+    <t>0.14 [0.03-0.25]
+0.13 [0.04-0.26]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.260
+ bk = -0.104</t>
   </si>
   <si>
     <t>NN_CMSY_Non-informative_r</t>
   </si>
   <si>
     <t>0.48 [0.10-1.50]
-0.14 [0.09-0.23]</t>
-  </si>
-  <si>
-    <t>23 [4-76]
-38 [23-58]</t>
-  </si>
-  <si>
-    <t>0.12 [0.02-0.22]
-0.12 [0.03-0.23]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.632
- bk = -0.047</t>
+0.14 [0.09-0.22]</t>
+  </si>
+  <si>
+    <t>29 [5-95]
+46 [30-68]</t>
+  </si>
+  <si>
+    <t>0.14 [0.03-0.25]
+0.16 [0.07-0.27]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.616
+ bk = 0.182</t>
   </si>
   <si>
     <t>zBRT_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.43 [0.20-0.80]
+0.24 [0.17-0.37]</t>
+  </si>
+  <si>
+    <t>24 [9-54]
+29 [20-38]</t>
+  </si>
+  <si>
+    <t>0.23 [0.01-0.45]
+0.25 [0.05-0.51]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.368
+ bk = -0.117</t>
+  </si>
+  <si>
+    <t>zBRT_lower resilience</t>
+  </si>
+  <si>
+    <t>61 [13-189]
+99 [58-150]</t>
+  </si>
+  <si>
+    <t>0.23 [0.01-0.45]
+0.29 [0.12-0.48]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.572
+ bk = 0.329</t>
+  </si>
+  <si>
+    <t>zBRT_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 [0.40-1.00]
+0.47 [0.35-0.63]</t>
+  </si>
+  <si>
+    <t>15 [6-29]
+17 [13-22]</t>
+  </si>
+  <si>
+    <t>0.23 [0.01-0.45]
+0.24 [0.06-0.52]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.239
+ bk = -0.095</t>
+  </si>
+  <si>
+    <t>zBRT_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.48 [0.10-1.50]
+0.15 [0.10-0.24]</t>
+  </si>
+  <si>
+    <t>29 [5-98]
+49 [31-72]</t>
+  </si>
+  <si>
+    <t>0.23 [0.01-0.45]
+0.27 [0.08-0.50]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.659
+ bk = 0.098</t>
+  </si>
+  <si>
+    <t>Target_switch_Euler-lotka methods</t>
   </si>
   <si>
     <t>0.42 [0.20-0.80]
 0.24 [0.17-0.35]</t>
   </si>
   <si>
-    <t>19 [7-43]
-22 [15-30]</t>
-  </si>
-  <si>
-    <t>0.20 [0.01-0.39]
-0.26 [0.04-0.55]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.411
- bk = -0.403</t>
-  </si>
-  <si>
-    <t>zBRT_lower resilience</t>
+    <t>23 [9-52]
+29 [20-38]</t>
+  </si>
+  <si>
+    <t>0.25 [0.01-0.50]
+0.27 [0.06-0.60]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.413
+ bk = -0.117</t>
+  </si>
+  <si>
+    <t>Target_switch_lower resilience</t>
   </si>
   <si>
     <t>0.21 [0.05-0.60]
 0.07 [0.05-0.12]</t>
   </si>
   <si>
-    <t>49 [10-154]
-86 [50-129]</t>
-  </si>
-  <si>
-    <t>0.20 [0.01-0.39]
-0.23 [0.06-0.42]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.574
- bk = 0.057</t>
-  </si>
-  <si>
-    <t>zBRT_Higher resilience</t>
+    <t>62 [12-192]
+104 [60-156]</t>
+  </si>
+  <si>
+    <t>0.26 [0.01-0.50]
+0.29 [0.11-0.50]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.585
+ bk = 0.297</t>
+  </si>
+  <si>
+    <t>Target_switch_Higher resilience</t>
   </si>
   <si>
     <t>0.65 [0.40-1.00]
 0.46 [0.35-0.63]</t>
   </si>
   <si>
-    <t>0.20 [0.01-0.39]
-0.18 [0.03-0.44]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.303
- bk = -0.215</t>
-  </si>
-  <si>
-    <t>zBRT_Non-informative_r</t>
+    <t>14 [6-29]
+17 [13-22]</t>
+  </si>
+  <si>
+    <t>0.25 [0.01-0.50]
+0.29 [0.07-0.55]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.291
+ bk = 0.004</t>
+  </si>
+  <si>
+    <t>Target_switch_Non-informative_r</t>
   </si>
   <si>
     <t>0.49 [0.10-1.50]
-0.14 [0.09-0.21]</t>
-  </si>
-  <si>
-    <t>24 [4-80]
-42 [25-63]</t>
-  </si>
-  <si>
-    <t>0.20 [0.01-0.39]
-0.23 [0.06-0.45]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.645
- bk = -0.044</t>
-  </si>
-  <si>
-    <t>Target_switch_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.42 [0.20-0.80]
-0.25 [0.18-0.37]</t>
-  </si>
-  <si>
-    <t>19 [7-42]
-21 [15-29]</t>
-  </si>
-  <si>
-    <t>0.45 [0.20-0.70]
-0.49 [0.27-0.70]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.413
- bk = 0.177</t>
-  </si>
-  <si>
-    <t>Target_switch_lower resilience</t>
-  </si>
-  <si>
-    <t>51 [10-156]
-88 [52-131]</t>
-  </si>
-  <si>
-    <t>0.45 [0.20-0.70]
-0.41 [0.23-0.59]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.594
- bk = 0.288</t>
-  </si>
-  <si>
-    <t>Target_switch_Higher resilience</t>
+0.14 [0.09-0.23]</t>
+  </si>
+  <si>
+    <t>29 [5-98]
+49 [31-74]</t>
+  </si>
+  <si>
+    <t>0.25 [0.01-0.50]
+0.31 [0.13-0.52]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.630
+ bk = 0.317</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.43 [0.20-0.80]
+0.25 [0.17-0.37]</t>
+  </si>
+  <si>
+    <t>24 [9-53]
+28 [20-38]</t>
+  </si>
+  <si>
+    <t>0.50 [0.01-1.00]
+0.38 [0.06-0.68]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.389
+ bk = 0.338</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_lower resilience</t>
+  </si>
+  <si>
+    <t>62 [12-191]
+102 [61-153]</t>
+  </si>
+  <si>
+    <t>0.50 [0.01-1.00]
+0.36 [0.14-0.61]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.590
+ bk = 0.609</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Higher resilience</t>
   </si>
   <si>
     <t>0.65 [0.40-1.00]
-0.45 [0.34-0.61]</t>
-  </si>
-  <si>
-    <t>0.45 [0.20-0.70]
-0.55 [0.24-0.77]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.303
- bk = -0.040</t>
-  </si>
-  <si>
-    <t>Target_switch_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.48 [0.10-1.50]
-0.14 [0.09-0.24]</t>
-  </si>
-  <si>
-    <t>24 [4-77]
-39 [22-58]</t>
-  </si>
-  <si>
-    <t>0.45 [0.20-0.70]
-0.42 [0.22-0.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.604
- bk = 0.247</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.42 [0.20-0.80]
-0.26 [0.18-0.39]</t>
-  </si>
-  <si>
-    <t>19 [7-43]
-21 [15-29]</t>
-  </si>
-  <si>
-    <t>0.51 [0.01-1.00]
-0.54 [0.19-0.87]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.387
- bk = 0.428</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_lower resilience</t>
-  </si>
-  <si>
-    <t>0.22 [0.05-0.60]
-0.08 [0.05-0.12]</t>
-  </si>
-  <si>
-    <t>49 [10-156]
-86 [51-128]</t>
-  </si>
-  <si>
-    <t>0.51 [0.01-1.00]
-0.36 [0.10-0.66]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.594
- bk = 0.458</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 [0.40-1.00]
-0.49 [0.35-0.68]</t>
-  </si>
-  <si>
-    <t>12 [5-23]
-12 [9-16]</t>
-  </si>
-  <si>
-    <t>0.51 [0.01-1.00]
-0.66 [0.23-0.95]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.188
- bk = 0.141</t>
+0.49 [0.36-0.68]</t>
+  </si>
+  <si>
+    <t>15 [6-28]
+16 [12-21]</t>
+  </si>
+  <si>
+    <t>0.50 [0.01-1.00]
+0.67 [0.24-0.93]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.232
+ bk = 0.292</t>
   </si>
   <si>
     <t>Uninformative_bk_Non-informative_r</t>
   </si>
   <si>
-    <t>0.49 [0.10-1.50]
-0.15 [0.10-0.25]</t>
-  </si>
-  <si>
-    <t>24 [4-80]
-41 [23-62]</t>
+    <t>29 [5-95]
+47 [30-69]</t>
   </si>
   <si>
     <t>0.50 [0.01-1.00]
-0.44 [0.09-0.75]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.631
- bk = 0.385</t>
+0.37 [0.08-0.61]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.619
+ bk = 0.422</t>
   </si>
 </sst>
 </file>
@@ -706,7 +706,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -726,7 +726,7 @@
         <v>15</v>
       </c>
       <c r="F3">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -746,7 +746,7 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -766,7 +766,7 @@
         <v>25</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -786,7 +786,7 @@
         <v>30</v>
       </c>
       <c r="F6">
-        <v>14.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -794,30 +794,30 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>34</v>
       </c>
-      <c r="E7" t="s">
-        <v>35</v>
-      </c>
       <c r="F7">
-        <v>14.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
         <v>36</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>38</v>
@@ -826,7 +826,7 @@
         <v>39</v>
       </c>
       <c r="F8">
-        <v>18.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -846,7 +846,7 @@
         <v>44</v>
       </c>
       <c r="F9">
-        <v>18.4</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -866,7 +866,7 @@
         <v>49</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -874,127 +874,127 @@
         <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11">
-        <v>26.2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F13">
-        <v>12.4</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F14">
-        <v>64.2</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15">
-        <v>68</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F16">
-        <v>58.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
         <v>80</v>
@@ -1006,7 +1006,7 @@
         <v>82</v>
       </c>
       <c r="F17">
-        <v>61.9</v>
+        <v>61.4</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/scenarios_summarize_by_scenario_macarellus_cmsy.xlsx
+++ b/Catch models/scenarios_summarize_by_scenario_macarellus_cmsy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="82">
   <si>
     <t>scenario</t>
   </si>
@@ -37,293 +37,289 @@
     <t>NN_CMSY_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.43 [0.20-0.80]
-0.24 [0.17-0.36]</t>
-  </si>
-  <si>
-    <t>23 [9-53]
-29 [20-37]</t>
+    <t>0.42 [0.20-0.80]
+0.24 [0.16-0.36]</t>
+  </si>
+  <si>
+    <t>23 [9-52]
+30 [21-40]</t>
   </si>
   <si>
     <t>0.14 [0.03-0.25]
-0.15 [0.04-0.29]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.392
- bk = -0.089</t>
+0.14 [0.05-0.26]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.359
+ bk = 0.020</t>
   </si>
   <si>
     <t>NN_CMSY_lower resilience</t>
   </si>
   <si>
     <t>0.21 [0.05-0.60]
-0.08 [0.05-0.12]</t>
-  </si>
-  <si>
-    <t>63 [12-198]
-107 [59-161]</t>
+0.07 [0.04-0.11]</t>
+  </si>
+  <si>
+    <t>61 [12-197]
+112 [65-169]</t>
   </si>
   <si>
     <t>0.14 [0.03-0.25]
-0.18 [0.08-0.31]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.586
- bk = 0.131</t>
+0.17 [0.07-0.30]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.590
+ bk = 0.110</t>
   </si>
   <si>
     <t>NN_CMSY_Higher resilience</t>
   </si>
   <si>
     <t>0.65 [0.40-1.00]
-0.47 [0.36-0.66]</t>
+0.47 [0.35-0.62]</t>
+  </si>
+  <si>
+    <t>14 [6-28]
+17 [13-22]</t>
+  </si>
+  <si>
+    <t>0.14 [0.03-0.25]
+0.13 [0.05-0.25]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.291
+ bk = -0.024</t>
+  </si>
+  <si>
+    <t>NN_CMSY_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.49 [0.10-1.50]
+0.13 [0.08-0.20]</t>
+  </si>
+  <si>
+    <t>29 [5-96]
+53 [35-78]</t>
+  </si>
+  <si>
+    <t>0.14 [0.03-0.25]
+0.14 [0.05-0.25]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.632
+ bk = 0.119</t>
+  </si>
+  <si>
+    <t>zBRT_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 [0.20-0.80]
+0.24 [0.17-0.34]</t>
+  </si>
+  <si>
+    <t>24 [9-54]
+31 [22-41]</t>
+  </si>
+  <si>
+    <t>0.23 [0.01-0.45]
+0.24 [0.05-0.48]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.436
+ bk = 0.003</t>
+  </si>
+  <si>
+    <t>zBRT_lower resilience</t>
+  </si>
+  <si>
+    <t>63 [13-197]
+113 [66-169]</t>
+  </si>
+  <si>
+    <t>0.23 [0.01-0.45]
+0.28 [0.11-0.48]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.587
+ bk = 0.288</t>
+  </si>
+  <si>
+    <t>zBRT_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 [0.40-1.00]
+0.47 [0.35-0.65]</t>
+  </si>
+  <si>
+    <t>15 [7-29]
+17 [13-22]</t>
+  </si>
+  <si>
+    <t>0.23 [0.01-0.45]
+0.22 [0.04-0.50]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.254
+ bk = -0.093</t>
+  </si>
+  <si>
+    <t>zBRT_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.49 [0.10-1.50]
+0.14 [0.09-0.21]</t>
+  </si>
+  <si>
+    <t>29 [5-97]
+55 [34-80]</t>
+  </si>
+  <si>
+    <t>0.23 [0.01-0.45]
+0.26 [0.09-0.49]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.651
+ bk = 0.154</t>
+  </si>
+  <si>
+    <t>Target_switch_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>24 [9-53]
+31 [21-41]</t>
+  </si>
+  <si>
+    <t>0.26 [0.01-0.50]
+0.26 [0.05-0.55]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.393
+ bk = -0.096</t>
+  </si>
+  <si>
+    <t>Target_switch_lower resilience</t>
+  </si>
+  <si>
+    <t>61 [12-192]
+110 [65-169]</t>
+  </si>
+  <si>
+    <t>0.25 [0.01-0.50]
+0.30 [0.10-0.47]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.593
+ bk = 0.305</t>
+  </si>
+  <si>
+    <t>Target_switch_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 [0.40-1.00]
+0.46 [0.34-0.64]</t>
   </si>
   <si>
     <t>14 [6-29]
-17 [13-21]</t>
-  </si>
-  <si>
-    <t>0.14 [0.03-0.25]
-0.13 [0.04-0.26]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.260
- bk = -0.104</t>
-  </si>
-  <si>
-    <t>NN_CMSY_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.48 [0.10-1.50]
-0.14 [0.09-0.22]</t>
-  </si>
-  <si>
-    <t>29 [5-95]
-46 [30-68]</t>
-  </si>
-  <si>
-    <t>0.14 [0.03-0.25]
-0.16 [0.07-0.27]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.616
- bk = 0.182</t>
-  </si>
-  <si>
-    <t>zBRT_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.43 [0.20-0.80]
-0.24 [0.17-0.37]</t>
-  </si>
-  <si>
-    <t>24 [9-54]
-29 [20-38]</t>
-  </si>
-  <si>
-    <t>0.23 [0.01-0.45]
-0.25 [0.05-0.51]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.368
- bk = -0.117</t>
-  </si>
-  <si>
-    <t>zBRT_lower resilience</t>
-  </si>
-  <si>
-    <t>61 [13-189]
-99 [58-150]</t>
-  </si>
-  <si>
-    <t>0.23 [0.01-0.45]
-0.29 [0.12-0.48]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.572
- bk = 0.329</t>
-  </si>
-  <si>
-    <t>zBRT_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 [0.40-1.00]
-0.47 [0.35-0.63]</t>
-  </si>
-  <si>
-    <t>15 [6-29]
-17 [13-22]</t>
-  </si>
-  <si>
-    <t>0.23 [0.01-0.45]
-0.24 [0.06-0.52]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.239
- bk = -0.095</t>
-  </si>
-  <si>
-    <t>zBRT_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.48 [0.10-1.50]
-0.15 [0.10-0.24]</t>
-  </si>
-  <si>
-    <t>29 [5-98]
-49 [31-72]</t>
-  </si>
-  <si>
-    <t>0.23 [0.01-0.45]
-0.27 [0.08-0.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.659
- bk = 0.098</t>
-  </si>
-  <si>
-    <t>Target_switch_Euler-lotka methods</t>
+17 [12-22]</t>
+  </si>
+  <si>
+    <t>0.25 [0.01-0.50]
+0.29 [0.05-0.63]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.216
+ bk = -0.125</t>
+  </si>
+  <si>
+    <t>Target_switch_Non-informative_r</t>
+  </si>
+  <si>
+    <t>29 [5-99]
+55 [35-81]</t>
+  </si>
+  <si>
+    <t>0.26 [0.01-0.50]
+0.30 [0.08-0.51]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.647
+ bk = 0.107</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Euler-lotka methods</t>
   </si>
   <si>
     <t>0.42 [0.20-0.80]
-0.24 [0.17-0.35]</t>
-  </si>
-  <si>
-    <t>23 [9-52]
-29 [20-38]</t>
-  </si>
-  <si>
-    <t>0.25 [0.01-0.50]
-0.27 [0.06-0.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.413
- bk = -0.117</t>
-  </si>
-  <si>
-    <t>Target_switch_lower resilience</t>
+0.25 [0.17-0.37]</t>
+  </si>
+  <si>
+    <t>24 [8-54]
+30 [21-41]</t>
+  </si>
+  <si>
+    <t>0.51 [0.01-1.00]
+0.41 [0.06-0.82]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.404
+ bk = 0.297</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_lower resilience</t>
   </si>
   <si>
     <t>0.21 [0.05-0.60]
 0.07 [0.05-0.12]</t>
   </si>
   <si>
-    <t>62 [12-192]
-104 [60-156]</t>
-  </si>
-  <si>
-    <t>0.26 [0.01-0.50]
-0.29 [0.11-0.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.585
- bk = 0.297</t>
-  </si>
-  <si>
-    <t>Target_switch_Higher resilience</t>
+    <t>61 [12-190]
+110 [65-164]</t>
+  </si>
+  <si>
+    <t>0.51 [0.01-1.00]
+0.34 [0.11-0.59]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.594
+ bk = 0.568</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Higher resilience</t>
   </si>
   <si>
     <t>0.65 [0.40-1.00]
-0.46 [0.35-0.63]</t>
-  </si>
-  <si>
-    <t>14 [6-29]
-17 [13-22]</t>
-  </si>
-  <si>
-    <t>0.25 [0.01-0.50]
-0.29 [0.07-0.55]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.291
- bk = 0.004</t>
-  </si>
-  <si>
-    <t>Target_switch_Non-informative_r</t>
+0.48 [0.36-0.67]</t>
+  </si>
+  <si>
+    <t>14 [6-28]
+17 [12-21]</t>
+  </si>
+  <si>
+    <t>0.50 [0.01-1.00]
+0.63 [0.08-0.95]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.252
+ bk = -0.024</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Non-informative_r</t>
   </si>
   <si>
     <t>0.49 [0.10-1.50]
-0.14 [0.09-0.23]</t>
+0.15 [0.10-0.23]</t>
   </si>
   <si>
     <t>29 [5-98]
-49 [31-74]</t>
-  </si>
-  <si>
-    <t>0.25 [0.01-0.50]
-0.31 [0.13-0.52]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.630
- bk = 0.317</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.43 [0.20-0.80]
-0.25 [0.17-0.37]</t>
-  </si>
-  <si>
-    <t>24 [9-53]
-28 [20-38]</t>
-  </si>
-  <si>
-    <t>0.50 [0.01-1.00]
-0.38 [0.06-0.68]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.389
- bk = 0.338</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_lower resilience</t>
-  </si>
-  <si>
-    <t>62 [12-191]
-102 [61-153]</t>
-  </si>
-  <si>
-    <t>0.50 [0.01-1.00]
-0.36 [0.14-0.61]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.590
- bk = 0.609</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 [0.40-1.00]
-0.49 [0.36-0.68]</t>
-  </si>
-  <si>
-    <t>15 [6-28]
-16 [12-21]</t>
-  </si>
-  <si>
-    <t>0.50 [0.01-1.00]
-0.67 [0.24-0.93]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.232
- bk = 0.292</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Non-informative_r</t>
-  </si>
-  <si>
-    <t>29 [5-95]
-47 [30-69]</t>
-  </si>
-  <si>
-    <t>0.50 [0.01-1.00]
-0.37 [0.08-0.61]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.619
- bk = 0.422</t>
+53 [32-78]</t>
+  </si>
+  <si>
+    <t>0.51 [0.01-1.00]
+0.36 [0.08-0.63]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.643
+ bk = 0.450</t>
   </si>
 </sst>
 </file>
@@ -706,7 +702,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -726,7 +722,7 @@
         <v>15</v>
       </c>
       <c r="F3">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -746,7 +742,7 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -766,7 +762,7 @@
         <v>25</v>
       </c>
       <c r="F5">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -786,7 +782,7 @@
         <v>30</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -806,7 +802,7 @@
         <v>34</v>
       </c>
       <c r="F7">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -826,7 +822,7 @@
         <v>39</v>
       </c>
       <c r="F8">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -846,7 +842,7 @@
         <v>44</v>
       </c>
       <c r="F9">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -854,56 +850,56 @@
         <v>45</v>
       </c>
       <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>46</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>47</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>48</v>
       </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
       <c r="F10">
-        <v>19.6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
         <v>50</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>54</v>
-      </c>
       <c r="F11">
-        <v>24</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="s">
         <v>55</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>56</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>57</v>
-      </c>
-      <c r="D12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
       </c>
       <c r="F12">
         <v>22.6</v>
@@ -911,102 +907,102 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="B13" t="s">
+      <c r="E13" t="s">
         <v>61</v>
       </c>
-      <c r="C13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" t="s">
-        <v>64</v>
-      </c>
       <c r="F13">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
         <v>65</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E14" t="s">
         <v>66</v>
       </c>
-      <c r="C14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" t="s">
-        <v>69</v>
-      </c>
       <c r="F14">
-        <v>62.4</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
         <v>70</v>
       </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>71</v>
       </c>
-      <c r="D15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" t="s">
-        <v>73</v>
-      </c>
       <c r="F15">
-        <v>67.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
         <v>74</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>75</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>76</v>
       </c>
-      <c r="D16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" t="s">
-        <v>78</v>
-      </c>
       <c r="F16">
-        <v>56.6</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" t="s">
         <v>79</v>
       </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>80</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>81</v>
       </c>
-      <c r="E17" t="s">
-        <v>82</v>
-      </c>
       <c r="F17">
-        <v>61.4</v>
+        <v>58.4</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/scenarios_summarize_by_scenario_macarellus_cmsy.xlsx
+++ b/Catch models/scenarios_summarize_by_scenario_macarellus_cmsy.xlsx
@@ -38,19 +38,19 @@
   </si>
   <si>
     <t>0.42 [0.20-0.80]
-0.24 [0.16-0.36]</t>
-  </si>
-  <si>
-    <t>23 [9-52]
-30 [21-40]</t>
+0.24 [0.17-0.36]</t>
+  </si>
+  <si>
+    <t>24 [8-53]
+30 [21-41]</t>
   </si>
   <si>
     <t>0.14 [0.03-0.25]
 0.14 [0.05-0.26]</t>
   </si>
   <si>
-    <t xml:space="preserve"> r = 0.359
- bk = 0.020</t>
+    <t xml:space="preserve"> r = 0.377
+ bk = 0.062</t>
   </si>
   <si>
     <t>NN_CMSY_lower resilience</t>
@@ -60,266 +60,266 @@
 0.07 [0.04-0.11]</t>
   </si>
   <si>
-    <t>61 [12-197]
-112 [65-169]</t>
+    <t>60 [12-191]
+107 [63-163]</t>
   </si>
   <si>
     <t>0.14 [0.03-0.25]
-0.17 [0.07-0.30]</t>
+0.17 [0.08-0.30]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.589
+ bk = 0.173</t>
+  </si>
+  <si>
+    <t>NN_CMSY_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 [0.40-1.00]
+0.47 [0.35-0.65]</t>
+  </si>
+  <si>
+    <t>14 [6-29]
+17 [13-22]</t>
+  </si>
+  <si>
+    <t>0.14 [0.03-0.25]
+0.14 [0.05-0.27]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.231
+ bk = -0.043</t>
+  </si>
+  <si>
+    <t>NN_CMSY_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.48 [0.10-1.50]
+0.13 [0.08-0.20]</t>
+  </si>
+  <si>
+    <t>29 [5-96]
+53 [34-78]</t>
+  </si>
+  <si>
+    <t>0.14 [0.03-0.25]
+0.16 [0.06-0.27]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.636
+ bk = 0.105</t>
+  </si>
+  <si>
+    <t>zBRT_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>24 [9-53]
+30 [20-40]</t>
+  </si>
+  <si>
+    <t>0.22 [0.01-0.44]
+0.21 [0.06-0.41]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.391
+ bk = 0.121</t>
+  </si>
+  <si>
+    <t>zBRT_lower resilience</t>
+  </si>
+  <si>
+    <t>61 [13-189]
+108 [63-163]</t>
+  </si>
+  <si>
+    <t>0.22 [0.01-0.44]
+0.26 [0.10-0.45]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.571
+ bk = 0.302</t>
+  </si>
+  <si>
+    <t>zBRT_Higher resilience</t>
+  </si>
+  <si>
+    <t>15 [6-29]
+17 [12-21]</t>
+  </si>
+  <si>
+    <t>0.23 [0.01-0.44]
+0.21 [0.05-0.50]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.275
+ bk = -0.089</t>
+  </si>
+  <si>
+    <t>zBRT_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.49 [0.10-1.50]
+0.13 [0.08-0.20]</t>
+  </si>
+  <si>
+    <t>29 [5-97]
+55 [35-79]</t>
+  </si>
+  <si>
+    <t>0.23 [0.01-0.44]
+0.24 [0.10-0.42]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.623
+ bk = 0.297</t>
+  </si>
+  <si>
+    <t>Target_switch_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 [0.20-0.80]
+0.24 [0.17-0.35]</t>
+  </si>
+  <si>
+    <t>24 [9-53]
+30 [21-40]</t>
+  </si>
+  <si>
+    <t>0.26 [0.01-0.50]
+0.27 [0.06-0.50]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.416
+ bk = 0.000</t>
+  </si>
+  <si>
+    <t>Target_switch_lower resilience</t>
+  </si>
+  <si>
+    <t>63 [13-192]
+111 [67-166]</t>
+  </si>
+  <si>
+    <t>0.25 [0.01-0.50]
+0.28 [0.12-0.45]</t>
   </si>
   <si>
     <t xml:space="preserve"> r = 0.590
- bk = 0.110</t>
-  </si>
-  <si>
-    <t>NN_CMSY_Higher resilience</t>
+ bk = 0.369</t>
+  </si>
+  <si>
+    <t>Target_switch_Higher resilience</t>
   </si>
   <si>
     <t>0.65 [0.40-1.00]
-0.47 [0.35-0.62]</t>
+0.46 [0.35-0.62]</t>
   </si>
   <si>
     <t>14 [6-28]
 17 [13-22]</t>
   </si>
   <si>
-    <t>0.14 [0.03-0.25]
-0.13 [0.05-0.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.291
- bk = -0.024</t>
-  </si>
-  <si>
-    <t>NN_CMSY_Non-informative_r</t>
+    <t>0.25 [0.01-0.50]
+0.24 [0.03-0.50]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.292
+ bk = -0.143</t>
+  </si>
+  <si>
+    <t>Target_switch_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.48 [0.10-1.50]
+0.14 [0.09-0.22]</t>
+  </si>
+  <si>
+    <t>29 [5-98]
+55 [34-80]</t>
+  </si>
+  <si>
+    <t>0.26 [0.01-0.50]
+0.28 [0.09-0.48]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.627
+ bk = 0.261</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 [0.20-0.80]
+0.25 [0.17-0.35]</t>
+  </si>
+  <si>
+    <t>24 [8-53]
+30 [22-41]</t>
+  </si>
+  <si>
+    <t>0.51 [0.01-1.00]
+0.38 [0.08-0.67]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.411
+ bk = 0.405</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_lower resilience</t>
+  </si>
+  <si>
+    <t>0.21 [0.05-0.60]
+0.07 [0.05-0.11]</t>
+  </si>
+  <si>
+    <t>65 [12-201]
+118 [71-175]</t>
+  </si>
+  <si>
+    <t>0.51 [0.01-1.00]
+0.32 [0.11-0.59]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.626
+ bk = 0.578</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 [0.40-1.00]
+0.48 [0.36-0.64]</t>
+  </si>
+  <si>
+    <t>14 [6-28]
+17 [13-21]</t>
+  </si>
+  <si>
+    <t>0.50 [0.01-1.00]
+0.47 [0.06-0.84]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.280
+ bk = 0.127</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Non-informative_r</t>
   </si>
   <si>
     <t>0.49 [0.10-1.50]
-0.13 [0.08-0.20]</t>
-  </si>
-  <si>
-    <t>29 [5-96]
-53 [35-78]</t>
-  </si>
-  <si>
-    <t>0.14 [0.03-0.25]
-0.14 [0.05-0.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.632
- bk = 0.119</t>
-  </si>
-  <si>
-    <t>zBRT_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.42 [0.20-0.80]
-0.24 [0.17-0.34]</t>
-  </si>
-  <si>
-    <t>24 [9-54]
-31 [22-41]</t>
-  </si>
-  <si>
-    <t>0.23 [0.01-0.45]
-0.24 [0.05-0.48]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.436
- bk = 0.003</t>
-  </si>
-  <si>
-    <t>zBRT_lower resilience</t>
-  </si>
-  <si>
-    <t>63 [13-197]
-113 [66-169]</t>
-  </si>
-  <si>
-    <t>0.23 [0.01-0.45]
-0.28 [0.11-0.48]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.587
- bk = 0.288</t>
-  </si>
-  <si>
-    <t>zBRT_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 [0.40-1.00]
-0.47 [0.35-0.65]</t>
-  </si>
-  <si>
-    <t>15 [7-29]
-17 [13-22]</t>
-  </si>
-  <si>
-    <t>0.23 [0.01-0.45]
-0.22 [0.04-0.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.254
- bk = -0.093</t>
-  </si>
-  <si>
-    <t>zBRT_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.49 [0.10-1.50]
-0.14 [0.09-0.21]</t>
+0.14 [0.09-0.22]</t>
   </si>
   <si>
     <t>29 [5-97]
-55 [34-80]</t>
-  </si>
-  <si>
-    <t>0.23 [0.01-0.45]
-0.26 [0.09-0.49]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.651
- bk = 0.154</t>
-  </si>
-  <si>
-    <t>Target_switch_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>24 [9-53]
-31 [21-41]</t>
-  </si>
-  <si>
-    <t>0.26 [0.01-0.50]
-0.26 [0.05-0.55]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.393
- bk = -0.096</t>
-  </si>
-  <si>
-    <t>Target_switch_lower resilience</t>
-  </si>
-  <si>
-    <t>61 [12-192]
-110 [65-169]</t>
-  </si>
-  <si>
-    <t>0.25 [0.01-0.50]
-0.30 [0.10-0.47]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.593
- bk = 0.305</t>
-  </si>
-  <si>
-    <t>Target_switch_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 [0.40-1.00]
-0.46 [0.34-0.64]</t>
-  </si>
-  <si>
-    <t>14 [6-29]
-17 [12-22]</t>
-  </si>
-  <si>
-    <t>0.25 [0.01-0.50]
-0.29 [0.05-0.63]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.216
- bk = -0.125</t>
-  </si>
-  <si>
-    <t>Target_switch_Non-informative_r</t>
-  </si>
-  <si>
-    <t>29 [5-99]
-55 [35-81]</t>
-  </si>
-  <si>
-    <t>0.26 [0.01-0.50]
-0.30 [0.08-0.51]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.647
- bk = 0.107</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.42 [0.20-0.80]
-0.25 [0.17-0.37]</t>
-  </si>
-  <si>
-    <t>24 [8-54]
-30 [21-41]</t>
-  </si>
-  <si>
-    <t>0.51 [0.01-1.00]
-0.41 [0.06-0.82]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.404
- bk = 0.297</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_lower resilience</t>
-  </si>
-  <si>
-    <t>0.21 [0.05-0.60]
-0.07 [0.05-0.12]</t>
-  </si>
-  <si>
-    <t>61 [12-190]
-110 [65-164]</t>
-  </si>
-  <si>
-    <t>0.51 [0.01-1.00]
-0.34 [0.11-0.59]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.594
- bk = 0.568</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 [0.40-1.00]
-0.48 [0.36-0.67]</t>
-  </si>
-  <si>
-    <t>14 [6-28]
-17 [12-21]</t>
+54 [33-79]</t>
   </si>
   <si>
     <t>0.50 [0.01-1.00]
-0.63 [0.08-0.95]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.252
- bk = -0.024</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.49 [0.10-1.50]
-0.15 [0.10-0.23]</t>
-  </si>
-  <si>
-    <t>29 [5-98]
-53 [32-78]</t>
-  </si>
-  <si>
-    <t>0.51 [0.01-1.00]
-0.36 [0.08-0.63]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r = 0.643
- bk = 0.450</t>
+0.33 [0.10-0.59]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> r = 0.636
+ bk = 0.547</t>
   </si>
 </sst>
 </file>
@@ -702,7 +702,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -722,7 +722,7 @@
         <v>15</v>
       </c>
       <c r="F3">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -742,7 +742,7 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -762,7 +762,7 @@
         <v>25</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -770,147 +770,147 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>29</v>
       </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
       <c r="F6">
-        <v>19.9</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
       <c r="F7">
-        <v>21.9</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
       <c r="F8">
-        <v>22.9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
         <v>40</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>42</v>
       </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>44</v>
-      </c>
       <c r="F9">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>47</v>
       </c>
-      <c r="E10" t="s">
-        <v>48</v>
-      </c>
       <c r="F10">
-        <v>21</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
         <v>50</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>51</v>
       </c>
-      <c r="E11" t="s">
-        <v>52</v>
-      </c>
       <c r="F11">
-        <v>25.8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
         <v>53</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>54</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>55</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>56</v>
       </c>
-      <c r="E12" t="s">
-        <v>57</v>
-      </c>
       <c r="F12">
-        <v>22.6</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
         <v>58</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
       </c>
       <c r="C13" t="s">
         <v>59</v>
@@ -922,7 +922,7 @@
         <v>61</v>
       </c>
       <c r="F13">
-        <v>23.3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -942,7 +942,7 @@
         <v>66</v>
       </c>
       <c r="F14">
-        <v>60.8</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -962,7 +962,7 @@
         <v>71</v>
       </c>
       <c r="F15">
-        <v>66.09999999999999</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1002,7 +1002,7 @@
         <v>81</v>
       </c>
       <c r="F17">
-        <v>58.4</v>
+        <v>60.3</v>
       </c>
     </row>
   </sheetData>
